--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486940_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486940_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7568</v>
+        <v>2.0228</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2225</v>
+        <v>1.4588</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5343</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>1.8493</v>
@@ -610,13 +610,13 @@
         <v>0.8214</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9488</v>
+        <v>-0.6828</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.527</v>
+        <v>-0.2906</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4218</v>
+        <v>-0.3922</v>
       </c>
       <c r="V2" t="n">
         <v>0.2402</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0702</v>
+        <v>1.0868</v>
       </c>
       <c r="E3" t="n">
-        <v>1.797</v>
+        <v>2.3472</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7269</v>
+        <v>-1.2604</v>
       </c>
       <c r="G3" t="n">
         <v>1.3254</v>
@@ -688,13 +688,13 @@
         <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8282</v>
+        <v>-0.8116</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9804</v>
+        <v>-0.4302</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1521</v>
+        <v>-0.3814</v>
       </c>
       <c r="V3" t="n">
         <v>-1.0698</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1561</v>
+        <v>0.1108</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2942</v>
+        <v>-0.3988</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4503</v>
+        <v>0.5095</v>
       </c>
       <c r="G4" t="n">
         <v>0.3442</v>
@@ -766,13 +766,13 @@
         <v>2.0534</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8554</v>
+        <v>-0.9008</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.159</v>
+        <v>-0.2636</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6965</v>
+        <v>-0.6372</v>
       </c>
       <c r="V4" t="n">
         <v>1.8993</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. VAZQUEZ VALLEJO</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4165</v>
+        <v>-0.745</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1388</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5553</v>
+        <v>-1.5641</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5715</v>
+        <v>1.9254</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9658</v>
+        <v>0.8364</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3943</v>
+        <v>1.089</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1464</v>
+        <v>3.0896</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5675</v>
+        <v>1.0512</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4211</v>
+        <v>2.0385</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5749</v>
+        <v>-1.1642</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3983</v>
+        <v>-0.2147</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9732</v>
+        <v>-0.9495</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4107</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q5" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3371</v>
+        <v>-1.6088</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0458</v>
+        <v>-0.2171</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3829</v>
+        <v>-1.3917</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2402</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>A. SMITH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0777</v>
+        <v>-0.8862</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7532</v>
+        <v>-1.347</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8309</v>
+        <v>0.4608</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9254</v>
+        <v>-0.9976</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8364</v>
+        <v>-1.6317</v>
       </c>
       <c r="I6" t="n">
-        <v>1.089</v>
+        <v>0.6341</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0896</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0512</v>
+        <v>-0.7718</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0385</v>
+        <v>0.0525</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1642</v>
+        <v>-0.2783</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2147</v>
+        <v>-0.8599</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9495</v>
+        <v>0.5816</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0534</v>
+        <v>-0.2053</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9414</v>
+        <v>-0.8804</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.283</v>
+        <v>-0.4224</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.6584</v>
+        <v>-0.4581</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2402</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SMITH</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0863</v>
+        <v>-1.1228</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5175</v>
+        <v>-1.924</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4312</v>
+        <v>0.8012</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9976</v>
+        <v>-0.5224</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6317</v>
+        <v>-0.3698</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6341</v>
+        <v>-0.1525</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7193000000000001</v>
+        <v>-0.599</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7718</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0525</v>
+        <v>0.0789</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2783</v>
+        <v>0.0766</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8599</v>
+        <v>0.308</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5816</v>
+        <v>-0.2314</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2321</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0805</v>
+        <v>-0.1898</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5928</v>
+        <v>-0.093</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4877</v>
+        <v>-0.0968</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>G. VAZQUEZ VALLEJO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1089</v>
+        <v>-1.4625</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0286</v>
+        <v>-0.9072</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9198</v>
+        <v>-0.5553</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5224</v>
+        <v>0.5715</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3698</v>
+        <v>1.9658</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1525</v>
+        <v>-1.3943</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.599</v>
+        <v>1.1464</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6778999999999999</v>
+        <v>1.5675</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0789</v>
+        <v>-0.4211</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0766</v>
+        <v>-0.5749</v>
       </c>
       <c r="N8" t="n">
-        <v>0.308</v>
+        <v>0.3983</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2314</v>
+        <v>-0.9732</v>
       </c>
       <c r="P8" t="n">
         <v>-0.4107</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2321</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1758</v>
+        <v>-1.3831</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1976</v>
+        <v>-0.0002</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0218</v>
+        <v>-1.3829</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1771</v>
+        <v>-2.4408</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2329</v>
+        <v>-3.5854</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0558</v>
+        <v>1.1447</v>
       </c>
       <c r="G9" t="n">
         <v>0.6182</v>
@@ -1156,13 +1156,13 @@
         <v>1.6427</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4831</v>
+        <v>-0.7468</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1045</v>
+        <v>-0.248</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5876</v>
+        <v>-0.4987</v>
       </c>
       <c r="V9" t="n">
         <v>1.1786</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4222</v>
+        <v>-4.2426</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7966</v>
+        <v>-0.5874</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.6256</v>
+        <v>-3.6552</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3758</v>
@@ -1234,13 +1234,13 @@
         <v>0.8214</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8329</v>
+        <v>-1.6533</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5192</v>
+        <v>-0.31</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3136</v>
+        <v>-1.3433</v>
       </c>
       <c r="V10" t="n">
         <v>-2.0082</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7351</v>
+        <v>-4.2616</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.183</v>
+        <v>-4.9466</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4479</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0.5387</v>
@@ -1312,13 +1312,13 @@
         <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7481</v>
+        <v>-1.2746</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8563</v>
+        <v>-0.62</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8918</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2402</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0627</v>
+        <v>-4.5035</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2673</v>
+        <v>-3.6784</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7954</v>
+        <v>-0.825</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9978</v>
@@ -1390,13 +1390,13 @@
         <v>1.2321</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2436</v>
+        <v>-1.6843</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0462</v>
+        <v>-0.4573</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1973</v>
+        <v>-1.227</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.1034</v>
+        <v>-16.4446</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.4086</v>
+        <v>-12.7497</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.694799999999999</v>
+        <v>-3.6948</v>
       </c>
       <c r="G13" t="n">
         <v>3.2791</v>
@@ -1453,13 +1453,13 @@
         <v>-4.1471</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.307999999999999</v>
+        <v>-2.308</v>
       </c>
       <c r="O13" t="n">
         <v>-1.8391</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.1871</v>
+        <v>-7.187099999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-21.5609</v>
@@ -1468,13 +1468,13 @@
         <v>14.374</v>
       </c>
       <c r="S13" t="n">
-        <v>-12.4749</v>
+        <v>-11.8163</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.0112</v>
+        <v>-3.3524</v>
       </c>
       <c r="U13" t="n">
-        <v>-8.463699999999999</v>
+        <v>-8.464</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7206999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.4938</v>
+        <v>7.5324</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1119</v>
+        <v>3.7521</v>
       </c>
       <c r="F14" t="n">
-        <v>4.3819</v>
+        <v>3.7803</v>
       </c>
       <c r="G14" t="n">
         <v>2.1844</v>
@@ -1546,13 +1546,13 @@
         <v>4.1068</v>
       </c>
       <c r="S14" t="n">
-        <v>5.4532</v>
+        <v>3.4917</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4982</v>
+        <v>2.1383</v>
       </c>
       <c r="U14" t="n">
-        <v>1.955</v>
+        <v>1.3534</v>
       </c>
       <c r="V14" t="n">
         <v>0.8295</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. MEDINA ROA</t>
+          <t>R. GARCIA SALAME</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1249</v>
+        <v>5.908</v>
       </c>
       <c r="E15" t="n">
-        <v>4.884</v>
+        <v>2.9233</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2409</v>
+        <v>2.9848</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0887</v>
+        <v>1.6976</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7359</v>
+        <v>-0.7784</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6472</v>
+        <v>2.476</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7409</v>
+        <v>2.1912</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6225</v>
+        <v>-0.9791</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1184</v>
+        <v>3.1703</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6522</v>
+        <v>-0.4936</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1134</v>
+        <v>0.2007</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.6943</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.8481</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0267</v>
+        <v>2.8748</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8103</v>
+        <v>1.8819</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4019</v>
+        <v>1.2783</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4084</v>
+        <v>0.6036</v>
       </c>
       <c r="V15" t="n">
-        <v>2.2259</v>
+        <v>0.4805</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7679</v>
+        <v>0.4805</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. GARCIA SALAME</t>
+          <t>E. MEDINA ROA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0513</v>
+        <v>5.302</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3542</v>
+        <v>3.9426</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6971</v>
+        <v>1.3594</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6976</v>
+        <v>1.0887</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7784</v>
+        <v>1.7359</v>
       </c>
       <c r="I16" t="n">
-        <v>2.476</v>
+        <v>-0.6472</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1912</v>
+        <v>1.7409</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9791</v>
+        <v>1.6225</v>
       </c>
       <c r="L16" t="n">
-        <v>3.1703</v>
+        <v>0.1184</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4936</v>
+        <v>-0.6522</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2007</v>
+        <v>0.1134</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6943</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8481</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8748</v>
+        <v>1.0267</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0252</v>
+        <v>1.9875</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2907</v>
+        <v>1.4605</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3159</v>
+        <v>0.527</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4805</v>
+        <v>2.2259</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4805</v>
+        <v>1.7679</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>K. CURFMAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9987</v>
+        <v>3.954</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5806</v>
+        <v>1.4235</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4181</v>
+        <v>2.5305</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5195</v>
+        <v>0.9117</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0931</v>
+        <v>2.2803</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4265</v>
+        <v>-1.3686</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1426</v>
+        <v>1.629</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3927</v>
+        <v>2.0244</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7498</v>
+        <v>-0.3954</v>
       </c>
       <c r="M17" t="n">
-        <v>0.377</v>
+        <v>-0.7174</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7004</v>
+        <v>0.2559</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3234</v>
+        <v>-0.9732</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4641</v>
+        <v>2.6694</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0418</v>
+        <v>1.1594</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4648</v>
+        <v>0.581</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.423</v>
+        <v>0.5784</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SANTANO BARTOLOME</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8283</v>
+        <v>3.1661</v>
       </c>
       <c r="E18" t="n">
-        <v>2.007</v>
+        <v>0.3714</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8213</v>
+        <v>2.7947</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9813</v>
+        <v>1.5195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.892</v>
+        <v>1.0931</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.8733</v>
+        <v>0.4265</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0204</v>
+        <v>1.1426</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3626</v>
+        <v>0.3927</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3422</v>
+        <v>0.7498</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0017</v>
+        <v>0.377</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4706</v>
+        <v>0.7004</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5311</v>
+        <v>-0.3234</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8481</v>
+        <v>1.4374</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8481</v>
+        <v>2.4641</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1792</v>
+        <v>0.2092</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2043</v>
+        <v>0.2556</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9749</v>
+        <v>-0.0464</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2177</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.2177</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. CURFMAN</t>
+          <t>J. SANTANO BARTOLOME</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5959</v>
+        <v>1.9775</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2729</v>
+        <v>1.2748</v>
       </c>
       <c r="F19" t="n">
-        <v>2.323</v>
+        <v>0.7027</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9117</v>
+        <v>-1.9813</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2803</v>
+        <v>0.892</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3686</v>
+        <v>-2.8733</v>
       </c>
       <c r="J19" t="n">
-        <v>1.629</v>
+        <v>0.0204</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0244</v>
+        <v>1.3626</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3954</v>
+        <v>-1.3422</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7174</v>
+        <v>-2.0017</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2559</v>
+        <v>-0.4706</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9732</v>
+        <v>-1.5311</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6694</v>
+        <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1988</v>
+        <v>2.3284</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5697</v>
+        <v>1.4721</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3709</v>
+        <v>0.8563</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2402</v>
+        <v>-0.2177</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2402</v>
+        <v>-0.2177</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0348</v>
+        <v>-0.6565</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5295</v>
+        <v>-2.3203</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4947</v>
+        <v>1.6638</v>
       </c>
       <c r="G20" t="n">
         <v>-3.4257</v>
@@ -2014,13 +2014,13 @@
         <v>3.4908</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1937</v>
+        <v>1.572</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7669</v>
+        <v>0.9761</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4268</v>
+        <v>0.5959</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2402</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6493</v>
+        <v>-2.9038</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0532</v>
+        <v>-1.367</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5961</v>
+        <v>-1.5368</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0099</v>
@@ -2092,13 +2092,13 @@
         <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5393</v>
+        <v>0.2847</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4339</v>
+        <v>0.1201</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1054</v>
+        <v>0.1647</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1786</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.3053</v>
+        <v>-6.4789</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.9331</v>
+        <v>-6.3055</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3722</v>
+        <v>-0.1734</v>
       </c>
       <c r="G22" t="n">
         <v>-3.2642</v>
@@ -2170,13 +2170,13 @@
         <v>2.0534</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5688</v>
+        <v>0.2576</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4457</v>
+        <v>0.182</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1231</v>
+        <v>0.0756</v>
       </c>
       <c r="V22" t="n">
         <v>-1.4189</v>
@@ -2203,25 +2203,25 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>17.1035</v>
+        <v>17.8008</v>
       </c>
       <c r="E23" t="n">
-        <v>3.694800000000003</v>
+        <v>3.694899999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>13.4087</v>
+        <v>14.106</v>
       </c>
       <c r="G23" t="n">
         <v>-3.2792</v>
       </c>
       <c r="H23" t="n">
-        <v>3.4567</v>
+        <v>3.456699999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-6.7359</v>
+        <v>-6.735900000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>4.147300000000001</v>
+        <v>4.1473</v>
       </c>
       <c r="K23" t="n">
         <v>2.3079</v>
@@ -2230,7 +2230,7 @@
         <v>1.8392</v>
       </c>
       <c r="M23" t="n">
-        <v>-7.426300000000001</v>
+        <v>-7.4263</v>
       </c>
       <c r="N23" t="n">
         <v>1.1489</v>
@@ -2248,19 +2248,19 @@
         <v>21.5608</v>
       </c>
       <c r="S23" t="n">
-        <v>12.4751</v>
+        <v>13.1724</v>
       </c>
       <c r="T23" t="n">
-        <v>8.463900000000001</v>
+        <v>8.464</v>
       </c>
       <c r="U23" t="n">
-        <v>4.0112</v>
+        <v>4.708499999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7207000000000001</v>
+        <v>0.7207000000000006</v>
       </c>
       <c r="W23" t="n">
-        <v>5.4577</v>
+        <v>5.457700000000001</v>
       </c>
       <c r="X23" t="n">
         <v>-4.7371</v>
